--- a/金融科技/data/NN5.xlsx
+++ b/金融科技/data/NN5.xlsx
@@ -5,20 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f5e7d8c14505f04/Desktop/學業筆記/金融科技/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f5e7d8c14505f04/Desktop/SCU_HW/金融科技/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_BD99B583C6B07E0F359B976A2F7D24CA1132F9D5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2748111E-A5D5-4AAD-9DD3-8226CA20ED92}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_BD99B583C6B07E0F359B976A2F7D24CA1132F9D5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9915AF8F-0EBF-4533-AD36-56120D66265F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="真實IC" sheetId="1" r:id="rId1"/>
     <sheet name="預測IC" sheetId="2" r:id="rId2"/>
-    <sheet name="NN勝率" sheetId="3" r:id="rId3"/>
-    <sheet name="NN累積報酬" sheetId="4" r:id="rId4"/>
-    <sheet name="NN夏普比率" sheetId="5" r:id="rId5"/>
-    <sheet name="NN樣本外R2" sheetId="6" r:id="rId6"/>
+    <sheet name="NN5勝率" sheetId="3" r:id="rId3"/>
+    <sheet name="NN5累積報酬" sheetId="4" r:id="rId4"/>
+    <sheet name="NN5夏普比率" sheetId="5" r:id="rId5"/>
+    <sheet name="NN5樣本外R2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -806,6 +806,9 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -814,9 +817,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2779,10 +2779,10 @@
       </c>
     </row>
     <row r="6" spans="1:136" s="6" customFormat="1" ht="17.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="28"/>
+      <c r="B6" s="29"/>
       <c r="C6" s="11">
         <v>2</v>
       </c>
@@ -3996,10 +3996,10 @@
     </row>
     <row r="9" spans="1:136" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:136" ht="17.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="B10" s="28"/>
+      <c r="B10" s="29"/>
       <c r="C10" s="13" t="s">
         <v>141</v>
       </c>
@@ -10181,7 +10181,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:137" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="27" t="s">
         <v>155</v>
       </c>
       <c r="B1" s="3"/>
@@ -11819,10 +11819,10 @@
       </c>
     </row>
     <row r="6" spans="1:137" s="6" customFormat="1" ht="17.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="30"/>
+      <c r="B6" s="31"/>
       <c r="C6" s="19">
         <v>2</v>
       </c>
@@ -13036,10 +13036,10 @@
     </row>
     <row r="9" spans="1:137" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:137" ht="17.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="B10" s="30"/>
+      <c r="B10" s="31"/>
       <c r="C10" s="20" t="s">
         <v>141</v>
       </c>
@@ -19220,7 +19220,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:138" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="27" t="s">
         <v>155</v>
       </c>
       <c r="B1" s="3"/>
@@ -20858,10 +20858,10 @@
       </c>
     </row>
     <row r="6" spans="1:138" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="30"/>
+      <c r="B6" s="31"/>
       <c r="C6" s="19">
         <v>2</v>
       </c>
@@ -22075,10 +22075,10 @@
     </row>
     <row r="9" spans="1:138" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:138" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="B10" s="30"/>
+      <c r="B10" s="31"/>
       <c r="C10" s="20" t="s">
         <v>141</v>
       </c>
@@ -28341,7 +28341,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:136" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="27" t="s">
         <v>155</v>
       </c>
       <c r="B1" s="3"/>
@@ -29979,10 +29979,10 @@
       </c>
     </row>
     <row r="6" spans="1:136" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="30"/>
+      <c r="B6" s="31"/>
       <c r="C6" s="19">
         <v>2</v>
       </c>
@@ -31196,10 +31196,10 @@
     </row>
     <row r="9" spans="1:136" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:136" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="B10" s="30"/>
+      <c r="B10" s="31"/>
       <c r="C10" s="20" t="s">
         <v>141</v>
       </c>
@@ -37378,7 +37378,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:139" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="27" t="s">
         <v>155</v>
       </c>
       <c r="B1" s="3"/>
@@ -39016,10 +39016,10 @@
       </c>
     </row>
     <row r="6" spans="1:139" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="30"/>
+      <c r="B6" s="31"/>
       <c r="C6" s="19">
         <v>2</v>
       </c>
@@ -40233,10 +40233,10 @@
     </row>
     <row r="9" spans="1:139" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:139" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="B10" s="30"/>
+      <c r="B10" s="31"/>
       <c r="C10" s="20" t="s">
         <v>141</v>
       </c>
@@ -46550,7 +46550,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:136" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="27" t="s">
         <v>155</v>
       </c>
       <c r="B1" s="3"/>
